--- a/Listing/CON02D.xlsx
+++ b/Listing/CON02D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="328">
   <si>
     <t/>
   </si>
@@ -115,6 +115,12 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
+    <t>20141002</t>
+  </si>
+  <si>
+    <t>WONHAE MTCHA BRY 30G</t>
+  </si>
+  <si>
     <t>20139890</t>
   </si>
   <si>
@@ -148,13 +154,13 @@
     <t>20033392</t>
   </si>
   <si>
-    <t>DELFI CHACHA MINIS30</t>
+    <t>DELFI CHACHA MINIS25</t>
   </si>
   <si>
     <t>20077110</t>
   </si>
   <si>
-    <t>CHACHA MINIS HATS 30</t>
+    <t>CHACHA MINIS HATS 25</t>
   </si>
   <si>
     <t>20122057</t>
@@ -310,22 +316,16 @@
     <t>SNICKERS CHOCO 35G</t>
   </si>
   <si>
-    <t>10000450</t>
-  </si>
-  <si>
-    <t>L`AGIE PEANUT PIE 30</t>
-  </si>
-  <si>
     <t>20054753</t>
   </si>
   <si>
-    <t>CADBURY FRUIT&amp;NUT 57</t>
+    <t>CADBURY FRUIT&amp;NUT 52</t>
   </si>
   <si>
     <t>20120257</t>
   </si>
   <si>
-    <t>CADBURY HAZELNUT 57G</t>
+    <t>CADBURY HAZELNUT 52G</t>
   </si>
   <si>
     <t>20054754</t>
@@ -334,16 +334,10 @@
     <t>CADBURY FRUIT&amp;NUT 30</t>
   </si>
   <si>
-    <t>20072368</t>
-  </si>
-  <si>
-    <t>CADBURY CSHW NUT 25G</t>
-  </si>
-  <si>
     <t>20134029</t>
   </si>
   <si>
-    <t>DELFI TRSURE MLK2X36</t>
+    <t>DELFI TRSURE MLK2X30</t>
   </si>
   <si>
     <t>20130547</t>
@@ -358,6 +352,12 @@
     <t>L'AGIE FULL MILK 60G</t>
   </si>
   <si>
+    <t>20141135</t>
+  </si>
+  <si>
+    <t>DARK WNDR ALMD 2X56G</t>
+  </si>
+  <si>
     <t>20133639</t>
   </si>
   <si>
@@ -406,6 +406,21 @@
     <t>SLVR QUEEN MATCHA 22</t>
   </si>
   <si>
+    <t>20141062</t>
+  </si>
+  <si>
+    <t>SQ CHUNKY CUPID 3X26</t>
+  </si>
+  <si>
+    <t>TG,(E-1B)</t>
+  </si>
+  <si>
+    <t>20141063</t>
+  </si>
+  <si>
+    <t>SQ CSHW BTRFLY 3X22G</t>
+  </si>
+  <si>
     <t>20140185</t>
   </si>
   <si>
@@ -415,9 +430,6 @@
     <t>10</t>
   </si>
   <si>
-    <t>TG,(E-1B)</t>
-  </si>
-  <si>
     <t>20130159</t>
   </si>
   <si>
@@ -640,12 +652,6 @@
     <t>MLKITA PUDD STRW 85G</t>
   </si>
   <si>
-    <t>20135479</t>
-  </si>
-  <si>
-    <t>FRUZZ CNDY BALL 25.5</t>
-  </si>
-  <si>
     <t>20129814</t>
   </si>
   <si>
@@ -793,12 +799,6 @@
     <t>SUGUS STICK BLCRNT30</t>
   </si>
   <si>
-    <t>20088545</t>
-  </si>
-  <si>
-    <t>MNTOS INR.CHEW GRP45</t>
-  </si>
-  <si>
     <t>20014081</t>
   </si>
   <si>
@@ -989,6 +989,12 @@
   </si>
   <si>
     <t>GO FRESS PRMINT 24'S</t>
+  </si>
+  <si>
+    <t>20141597</t>
+  </si>
+  <si>
+    <t>FRUZZ GUMMY ASORTD36</t>
   </si>
 </sst>
 </file>
@@ -1381,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1645,7 +1651,7 @@
         <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1665,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1685,7 +1691,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1693,10 +1699,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1705,7 +1711,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1713,19 +1719,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1745,7 +1751,7 @@
         <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1765,7 +1771,7 @@
         <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1785,7 +1791,7 @@
         <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1805,7 +1811,7 @@
         <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1825,7 +1831,7 @@
         <v>12</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1845,7 +1851,7 @@
         <v>12</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1865,7 +1871,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1882,10 +1888,10 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1905,7 +1911,7 @@
         <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1925,7 +1931,7 @@
         <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1945,7 +1951,7 @@
         <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1965,7 +1971,7 @@
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1985,30 +1991,30 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2025,7 +2031,7 @@
         <v>18</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -2045,7 +2051,7 @@
         <v>18</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -2065,7 +2071,7 @@
         <v>18</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -2085,7 +2091,7 @@
         <v>18</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2105,7 +2111,7 @@
         <v>18</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2122,21 +2128,21 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F37" s="1" t="s">
-        <v>87</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2145,10 +2151,10 @@
         <v>21</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2165,10 +2171,10 @@
         <v>21</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2185,18 +2191,18 @@
         <v>21</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2205,10 +2211,10 @@
         <v>21</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2225,7 +2231,7 @@
         <v>21</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>5</v>
@@ -2245,10 +2251,10 @@
         <v>21</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2325,7 +2331,7 @@
         <v>24</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>5</v>
@@ -2345,7 +2351,7 @@
         <v>24</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2365,10 +2371,10 @@
         <v>24</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2382,13 +2388,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2402,10 +2408,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2422,10 +2428,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2442,10 +2448,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2462,10 +2468,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2482,7 +2488,7 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>4</v>
@@ -2502,7 +2508,7 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>8</v>
@@ -2522,7 +2528,7 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>12</v>
@@ -2542,10 +2548,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2562,53 +2568,53 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2622,13 +2628,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2642,13 +2648,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2662,13 +2668,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2682,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2702,13 +2708,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2722,13 +2728,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2742,50 +2748,50 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2802,13 +2808,13 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2822,10 +2828,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2842,10 +2848,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2862,13 +2868,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2882,10 +2888,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2893,39 +2899,39 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>168</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2942,10 +2948,10 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2962,10 +2968,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>5</v>
@@ -2982,10 +2988,10 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -3002,10 +3008,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -3022,10 +3028,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -3042,10 +3048,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3053,19 +3059,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -3073,22 +3079,22 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3102,10 +3108,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3122,13 +3128,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3142,10 +3148,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3162,13 +3168,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3182,10 +3188,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3202,13 +3208,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3222,10 +3228,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3242,10 +3248,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3253,19 +3259,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>138</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3273,19 +3279,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3302,10 +3308,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3322,10 +3328,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3342,13 +3348,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3362,13 +3368,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3382,10 +3388,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3402,10 +3408,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3422,10 +3428,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3442,10 +3448,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3453,19 +3459,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3482,10 +3488,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3502,10 +3508,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>5</v>
@@ -3522,10 +3528,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3542,10 +3548,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3562,10 +3568,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3582,10 +3588,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3593,19 +3599,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3622,13 +3628,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3642,10 +3648,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>9</v>
@@ -3662,13 +3668,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3682,10 +3688,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3702,10 +3708,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3722,10 +3728,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3733,19 +3739,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3762,10 +3768,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3782,7 +3788,7 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>15</v>
@@ -3802,7 +3808,7 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>18</v>
@@ -3822,7 +3828,7 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>21</v>
@@ -3842,7 +3848,7 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>24</v>
@@ -3862,10 +3868,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>272</v>
@@ -3882,10 +3888,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>5</v>
@@ -3902,10 +3908,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>272</v>
@@ -4065,7 +4071,7 @@
         <v>279</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4085,7 +4091,7 @@
         <v>279</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4245,7 +4251,7 @@
         <v>299</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4265,7 +4271,7 @@
         <v>299</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4285,7 +4291,7 @@
         <v>299</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4305,7 +4311,7 @@
         <v>299</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4325,7 +4331,7 @@
         <v>299</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4345,7 +4351,7 @@
         <v>299</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4365,10 +4371,30 @@
         <v>299</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>288</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
